--- a/data/PLTR.xlsx
+++ b/data/PLTR.xlsx
@@ -39224,7 +39224,7 @@
         <v>46276.5625</v>
       </c>
       <c r="B1495" t="n">
-        <v>15177306</v>
+        <v>15383200</v>
       </c>
       <c r="C1495" t="n">
         <v>168.610000610352</v>
@@ -39233,7 +39233,7 @@
         <v>165.399993896484</v>
       </c>
       <c r="E1495" t="n">
-        <v>168</v>
+        <v>168.100006103516</v>
       </c>
       <c r="F1495" t="n">
         <v>167.229995727539</v>
@@ -39242,6 +39242,32 @@
         <v>167.229995727539</v>
       </c>
       <c r="H1495" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="A1496" s="1" t="n">
+        <v>46279.5625</v>
+      </c>
+      <c r="B1496" t="n">
+        <v>28989342</v>
+      </c>
+      <c r="C1496" t="n">
+        <v>174.359893798828</v>
+      </c>
+      <c r="D1496" t="n">
+        <v>166.419998168945</v>
+      </c>
+      <c r="E1496" t="n">
+        <v>169.699996948242</v>
+      </c>
+      <c r="F1496" t="n">
+        <v>173.309997558594</v>
+      </c>
+      <c r="G1496" t="n">
+        <v>173.309997558594</v>
+      </c>
+      <c r="H1496" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PLTR.xlsx
+++ b/data/PLTR.xlsx
@@ -39224,7 +39224,7 @@
         <v>46276.5625</v>
       </c>
       <c r="B1495" t="n">
-        <v>15383200</v>
+        <v>15410400</v>
       </c>
       <c r="C1495" t="n">
         <v>168.610000610352</v>
@@ -39250,16 +39250,16 @@
         <v>46279.5625</v>
       </c>
       <c r="B1496" t="n">
-        <v>28989342</v>
+        <v>29149500</v>
       </c>
       <c r="C1496" t="n">
-        <v>174.359893798828</v>
+        <v>174.360000610352</v>
       </c>
       <c r="D1496" t="n">
         <v>166.419998168945</v>
       </c>
       <c r="E1496" t="n">
-        <v>169.699996948242</v>
+        <v>169.695007324219</v>
       </c>
       <c r="F1496" t="n">
         <v>173.309997558594</v>
@@ -39268,6 +39268,32 @@
         <v>173.309997558594</v>
       </c>
       <c r="H1496" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1497">
+      <c r="A1497" s="1" t="n">
+        <v>46280.5625</v>
+      </c>
+      <c r="B1497" t="n">
+        <v>31164073</v>
+      </c>
+      <c r="C1497" t="n">
+        <v>176.589996337891</v>
+      </c>
+      <c r="D1497" t="n">
+        <v>169.449996948242</v>
+      </c>
+      <c r="E1497" t="n">
+        <v>170.5</v>
+      </c>
+      <c r="F1497" t="n">
+        <v>172.559997558594</v>
+      </c>
+      <c r="G1497" t="n">
+        <v>172.559997558594</v>
+      </c>
+      <c r="H1497" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PLTR.xlsx
+++ b/data/PLTR.xlsx
@@ -39276,7 +39276,7 @@
         <v>46280.5625</v>
       </c>
       <c r="B1497" t="n">
-        <v>31164073</v>
+        <v>31238200</v>
       </c>
       <c r="C1497" t="n">
         <v>176.589996337891</v>
@@ -39294,6 +39294,32 @@
         <v>172.559997558594</v>
       </c>
       <c r="H1497" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1498">
+      <c r="A1498" s="1" t="n">
+        <v>46281.5625</v>
+      </c>
+      <c r="B1498" t="n">
+        <v>20098723</v>
+      </c>
+      <c r="C1498" t="n">
+        <v>174.765106201172</v>
+      </c>
+      <c r="D1498" t="n">
+        <v>168.960006713867</v>
+      </c>
+      <c r="E1498" t="n">
+        <v>170.389999389648</v>
+      </c>
+      <c r="F1498" t="n">
+        <v>174.339996337891</v>
+      </c>
+      <c r="G1498" t="n">
+        <v>174.339996337891</v>
+      </c>
+      <c r="H1498" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PLTR.xlsx
+++ b/data/PLTR.xlsx
@@ -39302,10 +39302,10 @@
         <v>46281.5625</v>
       </c>
       <c r="B1498" t="n">
-        <v>20098723</v>
+        <v>20984000</v>
       </c>
       <c r="C1498" t="n">
-        <v>174.765106201172</v>
+        <v>174.764999389648</v>
       </c>
       <c r="D1498" t="n">
         <v>168.960006713867</v>
@@ -39320,6 +39320,32 @@
         <v>174.339996337891</v>
       </c>
       <c r="H1498" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1499">
+      <c r="A1499" s="1" t="n">
+        <v>46282.5625</v>
+      </c>
+      <c r="B1499" t="n">
+        <v>22869993</v>
+      </c>
+      <c r="C1499" t="n">
+        <v>177.880004882812</v>
+      </c>
+      <c r="D1499" t="n">
+        <v>172.606994628906</v>
+      </c>
+      <c r="E1499" t="n">
+        <v>175.759994506836</v>
+      </c>
+      <c r="F1499" t="n">
+        <v>176.240005493164</v>
+      </c>
+      <c r="G1499" t="n">
+        <v>176.240005493164</v>
+      </c>
+      <c r="H1499" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PLTR.xlsx
+++ b/data/PLTR.xlsx
@@ -39328,7 +39328,7 @@
         <v>46282.5625</v>
       </c>
       <c r="B1499" t="n">
-        <v>22869993</v>
+        <v>23776100</v>
       </c>
       <c r="C1499" t="n">
         <v>177.880004882812</v>
@@ -39337,7 +39337,7 @@
         <v>172.606994628906</v>
       </c>
       <c r="E1499" t="n">
-        <v>175.759994506836</v>
+        <v>175.949996948242</v>
       </c>
       <c r="F1499" t="n">
         <v>176.240005493164</v>
@@ -39346,6 +39346,32 @@
         <v>176.240005493164</v>
       </c>
       <c r="H1499" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="A1500" s="1" t="n">
+        <v>46283.5625</v>
+      </c>
+      <c r="B1500" t="n">
+        <v>38572181</v>
+      </c>
+      <c r="C1500" t="n">
+        <v>177.75</v>
+      </c>
+      <c r="D1500" t="n">
+        <v>172</v>
+      </c>
+      <c r="E1500" t="n">
+        <v>177.179992675781</v>
+      </c>
+      <c r="F1500" t="n">
+        <v>177.639999389648</v>
+      </c>
+      <c r="G1500" t="n">
+        <v>177.639999389648</v>
+      </c>
+      <c r="H1500" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PLTR.xlsx
+++ b/data/PLTR.xlsx
@@ -39354,7 +39354,7 @@
         <v>46283.5625</v>
       </c>
       <c r="B1500" t="n">
-        <v>38572181</v>
+        <v>39228600</v>
       </c>
       <c r="C1500" t="n">
         <v>177.75</v>
@@ -39372,6 +39372,32 @@
         <v>177.639999389648</v>
       </c>
       <c r="H1500" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1501">
+      <c r="A1501" s="1" t="n">
+        <v>46286.5625</v>
+      </c>
+      <c r="B1501" t="n">
+        <v>21901618</v>
+      </c>
+      <c r="C1501" t="n">
+        <v>183.380004882812</v>
+      </c>
+      <c r="D1501" t="n">
+        <v>176.759994506836</v>
+      </c>
+      <c r="E1501" t="n">
+        <v>178.725006103516</v>
+      </c>
+      <c r="F1501" t="n">
+        <v>183.089996337891</v>
+      </c>
+      <c r="G1501" t="n">
+        <v>183.089996337891</v>
+      </c>
+      <c r="H1501" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PLTR.xlsx
+++ b/data/PLTR.xlsx
@@ -39354,7 +39354,7 @@
         <v>46283.5625</v>
       </c>
       <c r="B1500" t="n">
-        <v>39228600</v>
+        <v>39302700</v>
       </c>
       <c r="C1500" t="n">
         <v>177.75</v>
@@ -39380,7 +39380,7 @@
         <v>46286.5625</v>
       </c>
       <c r="B1501" t="n">
-        <v>21901618</v>
+        <v>22006700</v>
       </c>
       <c r="C1501" t="n">
         <v>183.380004882812</v>
@@ -39398,6 +39398,32 @@
         <v>183.089996337891</v>
       </c>
       <c r="H1501" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="A1502" s="1" t="n">
+        <v>46287.5625</v>
+      </c>
+      <c r="B1502" t="n">
+        <v>21859169</v>
+      </c>
+      <c r="C1502" t="n">
+        <v>185.539993286133</v>
+      </c>
+      <c r="D1502" t="n">
+        <v>182.029998779297</v>
+      </c>
+      <c r="E1502" t="n">
+        <v>185.125</v>
+      </c>
+      <c r="F1502" t="n">
+        <v>184.990005493164</v>
+      </c>
+      <c r="G1502" t="n">
+        <v>184.990005493164</v>
+      </c>
+      <c r="H1502" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PLTR.xlsx
+++ b/data/PLTR.xlsx
@@ -39406,7 +39406,7 @@
         <v>46287.5625</v>
       </c>
       <c r="B1502" t="n">
-        <v>21859169</v>
+        <v>21991700</v>
       </c>
       <c r="C1502" t="n">
         <v>185.539993286133</v>
@@ -39424,6 +39424,32 @@
         <v>184.990005493164</v>
       </c>
       <c r="H1502" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1503">
+      <c r="A1503" s="1" t="n">
+        <v>46288.5625</v>
+      </c>
+      <c r="B1503" t="n">
+        <v>34908712</v>
+      </c>
+      <c r="C1503" t="n">
+        <v>193.789993286133</v>
+      </c>
+      <c r="D1503" t="n">
+        <v>182.949996948242</v>
+      </c>
+      <c r="E1503" t="n">
+        <v>186.220001220703</v>
+      </c>
+      <c r="F1503" t="n">
+        <v>191.789993286133</v>
+      </c>
+      <c r="G1503" t="n">
+        <v>191.789993286133</v>
+      </c>
+      <c r="H1503" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PLTR.xlsx
+++ b/data/PLTR.xlsx
@@ -39432,16 +39432,16 @@
         <v>46288.5625</v>
       </c>
       <c r="B1503" t="n">
-        <v>34908712</v>
+        <v>35119600</v>
       </c>
       <c r="C1503" t="n">
         <v>193.789993286133</v>
       </c>
       <c r="D1503" t="n">
-        <v>182.949996948242</v>
+        <v>182.940002441406</v>
       </c>
       <c r="E1503" t="n">
-        <v>186.220001220703</v>
+        <v>186.289993286133</v>
       </c>
       <c r="F1503" t="n">
         <v>191.789993286133</v>
@@ -39450,6 +39450,32 @@
         <v>191.789993286133</v>
       </c>
       <c r="H1503" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" s="1" t="n">
+        <v>46289.5625</v>
+      </c>
+      <c r="B1504" t="n">
+        <v>22612777</v>
+      </c>
+      <c r="C1504" t="n">
+        <v>194.679992675781</v>
+      </c>
+      <c r="D1504" t="n">
+        <v>188.240005493164</v>
+      </c>
+      <c r="E1504" t="n">
+        <v>189.199996948242</v>
+      </c>
+      <c r="F1504" t="n">
+        <v>192.589996337891</v>
+      </c>
+      <c r="G1504" t="n">
+        <v>192.589996337891</v>
+      </c>
+      <c r="H1504" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PLTR.xlsx
+++ b/data/PLTR.xlsx
@@ -39458,7 +39458,7 @@
         <v>46289.5625</v>
       </c>
       <c r="B1504" t="n">
-        <v>22612777</v>
+        <v>22675800</v>
       </c>
       <c r="C1504" t="n">
         <v>194.679992675781</v>
@@ -39476,6 +39476,32 @@
         <v>192.589996337891</v>
       </c>
       <c r="H1504" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="A1505" s="1" t="n">
+        <v>46290.5625</v>
+      </c>
+      <c r="B1505" t="n">
+        <v>17677784</v>
+      </c>
+      <c r="C1505" t="n">
+        <v>194.214004516602</v>
+      </c>
+      <c r="D1505" t="n">
+        <v>189.350006103516</v>
+      </c>
+      <c r="E1505" t="n">
+        <v>192.860000610352</v>
+      </c>
+      <c r="F1505" t="n">
+        <v>189.669998168945</v>
+      </c>
+      <c r="G1505" t="n">
+        <v>189.669998168945</v>
+      </c>
+      <c r="H1505" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PLTR.xlsx
+++ b/data/PLTR.xlsx
@@ -39484,7 +39484,7 @@
         <v>46290.5625</v>
       </c>
       <c r="B1505" t="n">
-        <v>17677784</v>
+        <v>17779900</v>
       </c>
       <c r="C1505" t="n">
         <v>194.214004516602</v>
@@ -39493,7 +39493,7 @@
         <v>189.350006103516</v>
       </c>
       <c r="E1505" t="n">
-        <v>192.860000610352</v>
+        <v>192.710006713867</v>
       </c>
       <c r="F1505" t="n">
         <v>189.669998168945</v>
@@ -39502,6 +39502,32 @@
         <v>189.669998168945</v>
       </c>
       <c r="H1505" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="A1506" s="1" t="n">
+        <v>46293.5625</v>
+      </c>
+      <c r="B1506" t="n">
+        <v>17374529</v>
+      </c>
+      <c r="C1506" t="n">
+        <v>190.25</v>
+      </c>
+      <c r="D1506" t="n">
+        <v>185.619995117188</v>
+      </c>
+      <c r="E1506" t="n">
+        <v>186.231002807617</v>
+      </c>
+      <c r="F1506" t="n">
+        <v>187.479995727539</v>
+      </c>
+      <c r="G1506" t="n">
+        <v>187.479995727539</v>
+      </c>
+      <c r="H1506" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PLTR.xlsx
+++ b/data/PLTR.xlsx
@@ -39484,7 +39484,7 @@
         <v>46290.5625</v>
       </c>
       <c r="B1505" t="n">
-        <v>17779900</v>
+        <v>17807100</v>
       </c>
       <c r="C1505" t="n">
         <v>194.214004516602</v>
@@ -39510,7 +39510,7 @@
         <v>46293.5625</v>
       </c>
       <c r="B1506" t="n">
-        <v>17374529</v>
+        <v>18464100</v>
       </c>
       <c r="C1506" t="n">
         <v>190.25</v>
@@ -39528,6 +39528,32 @@
         <v>187.479995727539</v>
       </c>
       <c r="H1506" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" s="1" t="n">
+        <v>46294.5625</v>
+      </c>
+      <c r="B1507" t="n">
+        <v>14094847</v>
+      </c>
+      <c r="C1507" t="n">
+        <v>188.630004882812</v>
+      </c>
+      <c r="D1507" t="n">
+        <v>184.809997558594</v>
+      </c>
+      <c r="E1507" t="n">
+        <v>187.339996337891</v>
+      </c>
+      <c r="F1507" t="n">
+        <v>186.970001220703</v>
+      </c>
+      <c r="G1507" t="n">
+        <v>186.970001220703</v>
+      </c>
+      <c r="H1507" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PLTR.xlsx
+++ b/data/PLTR.xlsx
@@ -39536,7 +39536,7 @@
         <v>46294.5625</v>
       </c>
       <c r="B1507" t="n">
-        <v>14094847</v>
+        <v>14754100</v>
       </c>
       <c r="C1507" t="n">
         <v>188.630004882812</v>
@@ -39554,6 +39554,32 @@
         <v>186.970001220703</v>
       </c>
       <c r="H1507" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" s="1" t="n">
+        <v>46295.5625</v>
+      </c>
+      <c r="B1508" t="n">
+        <v>16726991</v>
+      </c>
+      <c r="C1508" t="n">
+        <v>190.990005493164</v>
+      </c>
+      <c r="D1508" t="n">
+        <v>187</v>
+      </c>
+      <c r="E1508" t="n">
+        <v>187.929992675781</v>
+      </c>
+      <c r="F1508" t="n">
+        <v>187.050003051758</v>
+      </c>
+      <c r="G1508" t="n">
+        <v>187.050003051758</v>
+      </c>
+      <c r="H1508" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PLTR.xlsx
+++ b/data/PLTR.xlsx
@@ -39562,7 +39562,7 @@
         <v>46295.5625</v>
       </c>
       <c r="B1508" t="n">
-        <v>16726991</v>
+        <v>17921200</v>
       </c>
       <c r="C1508" t="n">
         <v>190.990005493164</v>
@@ -39571,7 +39571,7 @@
         <v>187</v>
       </c>
       <c r="E1508" t="n">
-        <v>187.929992675781</v>
+        <v>187.910003662109</v>
       </c>
       <c r="F1508" t="n">
         <v>187.050003051758</v>
@@ -39580,6 +39580,32 @@
         <v>187.050003051758</v>
       </c>
       <c r="H1508" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1509">
+      <c r="A1509" s="1" t="n">
+        <v>46296.5625</v>
+      </c>
+      <c r="B1509" t="n">
+        <v>17755532</v>
+      </c>
+      <c r="C1509" t="n">
+        <v>191.800003051758</v>
+      </c>
+      <c r="D1509" t="n">
+        <v>186.600006103516</v>
+      </c>
+      <c r="E1509" t="n">
+        <v>190.179992675781</v>
+      </c>
+      <c r="F1509" t="n">
+        <v>190.039993286133</v>
+      </c>
+      <c r="G1509" t="n">
+        <v>190.039993286133</v>
+      </c>
+      <c r="H1509" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PLTR.xlsx
+++ b/data/PLTR.xlsx
@@ -39588,7 +39588,7 @@
         <v>46296.5625</v>
       </c>
       <c r="B1509" t="n">
-        <v>17755532</v>
+        <v>17902000</v>
       </c>
       <c r="C1509" t="n">
         <v>191.800003051758</v>
@@ -39597,7 +39597,7 @@
         <v>186.600006103516</v>
       </c>
       <c r="E1509" t="n">
-        <v>190.179992675781</v>
+        <v>190.089996337891</v>
       </c>
       <c r="F1509" t="n">
         <v>190.039993286133</v>
@@ -39606,6 +39606,32 @@
         <v>190.039993286133</v>
       </c>
       <c r="H1509" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1510">
+      <c r="A1510" s="1" t="n">
+        <v>46297.5625</v>
+      </c>
+      <c r="B1510" t="n">
+        <v>17716878</v>
+      </c>
+      <c r="C1510" t="n">
+        <v>194.779998779297</v>
+      </c>
+      <c r="D1510" t="n">
+        <v>188.261199951172</v>
+      </c>
+      <c r="E1510" t="n">
+        <v>193.240005493164</v>
+      </c>
+      <c r="F1510" t="n">
+        <v>188.75</v>
+      </c>
+      <c r="G1510" t="n">
+        <v>188.75</v>
+      </c>
+      <c r="H1510" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PLTR.xlsx
+++ b/data/PLTR.xlsx
@@ -39614,16 +39614,16 @@
         <v>46297.5625</v>
       </c>
       <c r="B1510" t="n">
-        <v>17716878</v>
+        <v>17824100</v>
       </c>
       <c r="C1510" t="n">
         <v>194.779998779297</v>
       </c>
       <c r="D1510" t="n">
-        <v>188.261199951172</v>
+        <v>188.259994506836</v>
       </c>
       <c r="E1510" t="n">
-        <v>193.240005493164</v>
+        <v>193.029998779297</v>
       </c>
       <c r="F1510" t="n">
         <v>188.75</v>
@@ -39632,6 +39632,32 @@
         <v>188.75</v>
       </c>
       <c r="H1510" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1511">
+      <c r="A1511" s="1" t="n">
+        <v>46300.5625</v>
+      </c>
+      <c r="B1511" t="n">
+        <v>17670382</v>
+      </c>
+      <c r="C1511" t="n">
+        <v>192.689895629883</v>
+      </c>
+      <c r="D1511" t="n">
+        <v>187.630004882812</v>
+      </c>
+      <c r="E1511" t="n">
+        <v>189.149993896484</v>
+      </c>
+      <c r="F1511" t="n">
+        <v>189.399993896484</v>
+      </c>
+      <c r="G1511" t="n">
+        <v>189.399993896484</v>
+      </c>
+      <c r="H1511" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PLTR.xlsx
+++ b/data/PLTR.xlsx
@@ -39614,7 +39614,7 @@
         <v>46297.5625</v>
       </c>
       <c r="B1510" t="n">
-        <v>17824100</v>
+        <v>17932100</v>
       </c>
       <c r="C1510" t="n">
         <v>194.779998779297</v>
@@ -39640,16 +39640,16 @@
         <v>46300.5625</v>
       </c>
       <c r="B1511" t="n">
-        <v>17670382</v>
+        <v>17710000</v>
       </c>
       <c r="C1511" t="n">
-        <v>192.689895629883</v>
+        <v>192.690002441406</v>
       </c>
       <c r="D1511" t="n">
         <v>187.630004882812</v>
       </c>
       <c r="E1511" t="n">
-        <v>189.149993896484</v>
+        <v>189.449996948242</v>
       </c>
       <c r="F1511" t="n">
         <v>189.399993896484</v>
@@ -39658,6 +39658,32 @@
         <v>189.399993896484</v>
       </c>
       <c r="H1511" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1512">
+      <c r="A1512" s="1" t="n">
+        <v>46301.5625</v>
+      </c>
+      <c r="B1512" t="n">
+        <v>17488501</v>
+      </c>
+      <c r="C1512" t="n">
+        <v>194.559997558594</v>
+      </c>
+      <c r="D1512" t="n">
+        <v>190.25</v>
+      </c>
+      <c r="E1512" t="n">
+        <v>191</v>
+      </c>
+      <c r="F1512" t="n">
+        <v>192.070007324219</v>
+      </c>
+      <c r="G1512" t="n">
+        <v>192.070007324219</v>
+      </c>
+      <c r="H1512" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PLTR.xlsx
+++ b/data/PLTR.xlsx
@@ -39666,16 +39666,16 @@
         <v>46301.5625</v>
       </c>
       <c r="B1512" t="n">
-        <v>17488501</v>
+        <v>17651200</v>
       </c>
       <c r="C1512" t="n">
         <v>194.559997558594</v>
       </c>
       <c r="D1512" t="n">
-        <v>190.25</v>
+        <v>190.220001220703</v>
       </c>
       <c r="E1512" t="n">
-        <v>191</v>
+        <v>191.044998168945</v>
       </c>
       <c r="F1512" t="n">
         <v>192.070007324219</v>
@@ -39684,6 +39684,32 @@
         <v>192.070007324219</v>
       </c>
       <c r="H1512" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1513">
+      <c r="A1513" s="1" t="n">
+        <v>46302.5625</v>
+      </c>
+      <c r="B1513" t="n">
+        <v>15675589</v>
+      </c>
+      <c r="C1513" t="n">
+        <v>194.699996948242</v>
+      </c>
+      <c r="D1513" t="n">
+        <v>190.111999511719</v>
+      </c>
+      <c r="E1513" t="n">
+        <v>192.699996948242</v>
+      </c>
+      <c r="F1513" t="n">
+        <v>194.119995117188</v>
+      </c>
+      <c r="G1513" t="n">
+        <v>194.119995117188</v>
+      </c>
+      <c r="H1513" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PLTR.xlsx
+++ b/data/PLTR.xlsx
@@ -39692,7 +39692,7 @@
         <v>46302.5625</v>
       </c>
       <c r="B1513" t="n">
-        <v>15675589</v>
+        <v>15729200</v>
       </c>
       <c r="C1513" t="n">
         <v>194.699996948242</v>
@@ -39701,7 +39701,7 @@
         <v>190.111999511719</v>
       </c>
       <c r="E1513" t="n">
-        <v>192.699996948242</v>
+        <v>192.705001831055</v>
       </c>
       <c r="F1513" t="n">
         <v>194.119995117188</v>
@@ -39710,6 +39710,32 @@
         <v>194.119995117188</v>
       </c>
       <c r="H1513" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1514">
+      <c r="A1514" s="1" t="n">
+        <v>46303.5625</v>
+      </c>
+      <c r="B1514" t="n">
+        <v>41744992</v>
+      </c>
+      <c r="C1514" t="n">
+        <v>204.440002441406</v>
+      </c>
+      <c r="D1514" t="n">
+        <v>195.649993896484</v>
+      </c>
+      <c r="E1514" t="n">
+        <v>199</v>
+      </c>
+      <c r="F1514" t="n">
+        <v>198.779998779297</v>
+      </c>
+      <c r="G1514" t="n">
+        <v>198.779998779297</v>
+      </c>
+      <c r="H1514" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PLTR.xlsx
+++ b/data/PLTR.xlsx
@@ -39718,7 +39718,7 @@
         <v>46303.5625</v>
       </c>
       <c r="B1514" t="n">
-        <v>41744992</v>
+        <v>41865400</v>
       </c>
       <c r="C1514" t="n">
         <v>204.440002441406</v>
@@ -39736,6 +39736,32 @@
         <v>198.779998779297</v>
       </c>
       <c r="H1514" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1515">
+      <c r="A1515" s="1" t="n">
+        <v>46304.5625</v>
+      </c>
+      <c r="B1515" t="n">
+        <v>37389859</v>
+      </c>
+      <c r="C1515" t="n">
+        <v>209.300003051758</v>
+      </c>
+      <c r="D1515" t="n">
+        <v>198.300003051758</v>
+      </c>
+      <c r="E1515" t="n">
+        <v>201.059997558594</v>
+      </c>
+      <c r="F1515" t="n">
+        <v>209.050003051758</v>
+      </c>
+      <c r="G1515" t="n">
+        <v>209.050003051758</v>
+      </c>
+      <c r="H1515" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PLTR.xlsx
+++ b/data/PLTR.xlsx
@@ -39744,16 +39744,16 @@
         <v>46304.5625</v>
       </c>
       <c r="B1515" t="n">
-        <v>37389859</v>
+        <v>37479600</v>
       </c>
       <c r="C1515" t="n">
-        <v>209.300003051758</v>
+        <v>209.580001831055</v>
       </c>
       <c r="D1515" t="n">
         <v>198.300003051758</v>
       </c>
       <c r="E1515" t="n">
-        <v>201.059997558594</v>
+        <v>201.475006103516</v>
       </c>
       <c r="F1515" t="n">
         <v>209.050003051758</v>

--- a/data/PLTR.xlsx
+++ b/data/PLTR.xlsx
@@ -39796,16 +39796,16 @@
         <v>46308.5625</v>
       </c>
       <c r="B1517" t="n">
-        <v>18438992</v>
+        <v>18535900</v>
       </c>
       <c r="C1517" t="n">
-        <v>210.879898071289</v>
+        <v>210.880004882812</v>
       </c>
       <c r="D1517" t="n">
         <v>205.970001220703</v>
       </c>
       <c r="E1517" t="n">
-        <v>207.899993896484</v>
+        <v>208.080001831055</v>
       </c>
       <c r="F1517" t="n">
         <v>208.669998168945</v>
@@ -39814,6 +39814,32 @@
         <v>208.669998168945</v>
       </c>
       <c r="H1517" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1518">
+      <c r="A1518" s="1" t="n">
+        <v>46309.5625</v>
+      </c>
+      <c r="B1518" t="n">
+        <v>23930226</v>
+      </c>
+      <c r="C1518" t="n">
+        <v>209.279998779297</v>
+      </c>
+      <c r="D1518" t="n">
+        <v>199.740005493164</v>
+      </c>
+      <c r="E1518" t="n">
+        <v>207.360000610352</v>
+      </c>
+      <c r="F1518" t="n">
+        <v>200.970001220703</v>
+      </c>
+      <c r="G1518" t="n">
+        <v>200.970001220703</v>
+      </c>
+      <c r="H1518" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PLTR.xlsx
+++ b/data/PLTR.xlsx
@@ -39822,16 +39822,16 @@
         <v>46309.5625</v>
       </c>
       <c r="B1518" t="n">
-        <v>23930226</v>
+        <v>24263800</v>
       </c>
       <c r="C1518" t="n">
-        <v>209.279998779297</v>
+        <v>209.289993286133</v>
       </c>
       <c r="D1518" t="n">
         <v>199.740005493164</v>
       </c>
       <c r="E1518" t="n">
-        <v>207.360000610352</v>
+        <v>207.020004272461</v>
       </c>
       <c r="F1518" t="n">
         <v>200.970001220703</v>
@@ -39840,6 +39840,32 @@
         <v>200.970001220703</v>
       </c>
       <c r="H1518" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1519">
+      <c r="A1519" s="1" t="n">
+        <v>46310.5625</v>
+      </c>
+      <c r="B1519" t="n">
+        <v>24679424</v>
+      </c>
+      <c r="C1519" t="n">
+        <v>200.910003662109</v>
+      </c>
+      <c r="D1519" t="n">
+        <v>192.600006103516</v>
+      </c>
+      <c r="E1519" t="n">
+        <v>196.580001831055</v>
+      </c>
+      <c r="F1519" t="n">
+        <v>200.5</v>
+      </c>
+      <c r="G1519" t="n">
+        <v>200.5</v>
+      </c>
+      <c r="H1519" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PLTR.xlsx
+++ b/data/PLTR.xlsx
@@ -39848,7 +39848,7 @@
         <v>46310.5625</v>
       </c>
       <c r="B1519" t="n">
-        <v>24679424</v>
+        <v>24781500</v>
       </c>
       <c r="C1519" t="n">
         <v>200.910003662109</v>
@@ -39857,7 +39857,7 @@
         <v>192.600006103516</v>
       </c>
       <c r="E1519" t="n">
-        <v>196.580001831055</v>
+        <v>196.850006103516</v>
       </c>
       <c r="F1519" t="n">
         <v>200.5</v>
@@ -39866,6 +39866,32 @@
         <v>200.5</v>
       </c>
       <c r="H1519" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1520">
+      <c r="A1520" s="1" t="n">
+        <v>46311.5625</v>
+      </c>
+      <c r="B1520" t="n">
+        <v>32915752</v>
+      </c>
+      <c r="C1520" t="n">
+        <v>203.550003051758</v>
+      </c>
+      <c r="D1520" t="n">
+        <v>184.449996948242</v>
+      </c>
+      <c r="E1520" t="n">
+        <v>202.358993530273</v>
+      </c>
+      <c r="F1520" t="n">
+        <v>186.029998779297</v>
+      </c>
+      <c r="G1520" t="n">
+        <v>186.029998779297</v>
+      </c>
+      <c r="H1520" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PLTR.xlsx
+++ b/data/PLTR.xlsx
@@ -44452,7 +44452,7 @@
         <v>186.029998779297</v>
       </c>
       <c r="H1520" t="n">
-        <v>33253300</v>
+        <v>33354900</v>
       </c>
       <c r="I1520" t="s">
         <v>9</v>
@@ -44466,7 +44466,7 @@
         <v>46314.5625</v>
       </c>
       <c r="C1521" t="n">
-        <v>187</v>
+        <v>186.994995117188</v>
       </c>
       <c r="D1521" t="n">
         <v>196.990005493164</v>
@@ -44481,9 +44481,38 @@
         <v>194.149993896484</v>
       </c>
       <c r="H1521" t="n">
-        <v>23719536</v>
+        <v>23934800</v>
       </c>
       <c r="I1521" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1522">
+      <c r="A1522" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1522" s="1" t="n">
+        <v>46315.5625</v>
+      </c>
+      <c r="C1522" t="n">
+        <v>192.440002441406</v>
+      </c>
+      <c r="D1522" t="n">
+        <v>196.110000610352</v>
+      </c>
+      <c r="E1522" t="n">
+        <v>189.419998168945</v>
+      </c>
+      <c r="F1522" t="n">
+        <v>192.600006103516</v>
+      </c>
+      <c r="G1522" t="n">
+        <v>192.600006103516</v>
+      </c>
+      <c r="H1522" t="n">
+        <v>14979559</v>
+      </c>
+      <c r="I1522" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PLTR.xlsx
+++ b/data/PLTR.xlsx
@@ -44510,9 +44510,38 @@
         <v>192.600006103516</v>
       </c>
       <c r="H1522" t="n">
-        <v>14979559</v>
+        <v>15095200</v>
       </c>
       <c r="I1522" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1523">
+      <c r="A1523" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1523" s="1" t="n">
+        <v>46316.5625</v>
+      </c>
+      <c r="C1523" t="n">
+        <v>191.449996948242</v>
+      </c>
+      <c r="D1523" t="n">
+        <v>202.550003051758</v>
+      </c>
+      <c r="E1523" t="n">
+        <v>189.880004882812</v>
+      </c>
+      <c r="F1523" t="n">
+        <v>201.720001220703</v>
+      </c>
+      <c r="G1523" t="n">
+        <v>201.720001220703</v>
+      </c>
+      <c r="H1523" t="n">
+        <v>21192659</v>
+      </c>
+      <c r="I1523" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PLTR.xlsx
+++ b/data/PLTR.xlsx
@@ -44524,7 +44524,7 @@
         <v>46316.5625</v>
       </c>
       <c r="C1523" t="n">
-        <v>191.449996948242</v>
+        <v>191.720001220703</v>
       </c>
       <c r="D1523" t="n">
         <v>202.550003051758</v>
@@ -44539,9 +44539,38 @@
         <v>201.720001220703</v>
       </c>
       <c r="H1523" t="n">
-        <v>21192659</v>
+        <v>21398400</v>
       </c>
       <c r="I1523" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1524">
+      <c r="A1524" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1524" s="1" t="n">
+        <v>46317.5625</v>
+      </c>
+      <c r="C1524" t="n">
+        <v>200.979995727539</v>
+      </c>
+      <c r="D1524" t="n">
+        <v>202.630004882812</v>
+      </c>
+      <c r="E1524" t="n">
+        <v>194.535003662109</v>
+      </c>
+      <c r="F1524" t="n">
+        <v>196.190002441406</v>
+      </c>
+      <c r="G1524" t="n">
+        <v>196.190002441406</v>
+      </c>
+      <c r="H1524" t="n">
+        <v>22824523</v>
+      </c>
+      <c r="I1524" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PLTR.xlsx
+++ b/data/PLTR.xlsx
@@ -44553,7 +44553,7 @@
         <v>46317.5625</v>
       </c>
       <c r="C1524" t="n">
-        <v>200.979995727539</v>
+        <v>200.759994506836</v>
       </c>
       <c r="D1524" t="n">
         <v>202.630004882812</v>
@@ -44568,9 +44568,38 @@
         <v>196.190002441406</v>
       </c>
       <c r="H1524" t="n">
-        <v>22824523</v>
+        <v>22933600</v>
       </c>
       <c r="I1524" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1525">
+      <c r="A1525" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1525" s="1" t="n">
+        <v>46318.5625</v>
+      </c>
+      <c r="C1525" t="n">
+        <v>195.020004272461</v>
+      </c>
+      <c r="D1525" t="n">
+        <v>197.490005493164</v>
+      </c>
+      <c r="E1525" t="n">
+        <v>190.570205688477</v>
+      </c>
+      <c r="F1525" t="n">
+        <v>196.75</v>
+      </c>
+      <c r="G1525" t="n">
+        <v>196.75</v>
+      </c>
+      <c r="H1525" t="n">
+        <v>16072134</v>
+      </c>
+      <c r="I1525" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PLTR.xlsx
+++ b/data/PLTR.xlsx
@@ -44588,7 +44588,7 @@
         <v>197.490005493164</v>
       </c>
       <c r="E1525" t="n">
-        <v>190.570205688477</v>
+        <v>190.570007324219</v>
       </c>
       <c r="F1525" t="n">
         <v>196.75</v>
@@ -44597,9 +44597,38 @@
         <v>196.75</v>
       </c>
       <c r="H1525" t="n">
-        <v>16072134</v>
+        <v>17614200</v>
       </c>
       <c r="I1525" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1526">
+      <c r="A1526" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1526" s="1" t="n">
+        <v>46321.5625</v>
+      </c>
+      <c r="C1526" t="n">
+        <v>198.100006103516</v>
+      </c>
+      <c r="D1526" t="n">
+        <v>200.050003051758</v>
+      </c>
+      <c r="E1526" t="n">
+        <v>192.910003662109</v>
+      </c>
+      <c r="F1526" t="n">
+        <v>198.839996337891</v>
+      </c>
+      <c r="G1526" t="n">
+        <v>198.839996337891</v>
+      </c>
+      <c r="H1526" t="n">
+        <v>16326332</v>
+      </c>
+      <c r="I1526" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PLTR.xlsx
+++ b/data/PLTR.xlsx
@@ -44597,7 +44597,7 @@
         <v>196.75</v>
       </c>
       <c r="H1525" t="n">
-        <v>17614200</v>
+        <v>17668400</v>
       </c>
       <c r="I1525" t="s">
         <v>9</v>
@@ -44611,7 +44611,7 @@
         <v>46321.5625</v>
       </c>
       <c r="C1526" t="n">
-        <v>198.100006103516</v>
+        <v>197.899993896484</v>
       </c>
       <c r="D1526" t="n">
         <v>200.050003051758</v>
@@ -44626,9 +44626,38 @@
         <v>198.839996337891</v>
       </c>
       <c r="H1526" t="n">
-        <v>16326332</v>
+        <v>16380400</v>
       </c>
       <c r="I1526" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1527">
+      <c r="A1527" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1527" s="1" t="n">
+        <v>46322.5625</v>
+      </c>
+      <c r="C1527" t="n">
+        <v>198.020004272461</v>
+      </c>
+      <c r="D1527" t="n">
+        <v>201.830001831055</v>
+      </c>
+      <c r="E1527" t="n">
+        <v>196.789993286133</v>
+      </c>
+      <c r="F1527" t="n">
+        <v>198.729995727539</v>
+      </c>
+      <c r="G1527" t="n">
+        <v>198.729995727539</v>
+      </c>
+      <c r="H1527" t="n">
+        <v>19170693</v>
+      </c>
+      <c r="I1527" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PLTR.xlsx
+++ b/data/PLTR.xlsx
@@ -44640,7 +44640,7 @@
         <v>46322.5625</v>
       </c>
       <c r="C1527" t="n">
-        <v>198.020004272461</v>
+        <v>198.119995117188</v>
       </c>
       <c r="D1527" t="n">
         <v>201.830001831055</v>
@@ -44655,9 +44655,38 @@
         <v>198.729995727539</v>
       </c>
       <c r="H1527" t="n">
-        <v>19170693</v>
+        <v>19907300</v>
       </c>
       <c r="I1527" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1528">
+      <c r="A1528" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1528" s="1" t="n">
+        <v>46323.5625</v>
+      </c>
+      <c r="C1528" t="n">
+        <v>197.009994506836</v>
+      </c>
+      <c r="D1528" t="n">
+        <v>198.720001220703</v>
+      </c>
+      <c r="E1528" t="n">
+        <v>193.130599975586</v>
+      </c>
+      <c r="F1528" t="n">
+        <v>196.809997558594</v>
+      </c>
+      <c r="G1528" t="n">
+        <v>196.809997558594</v>
+      </c>
+      <c r="H1528" t="n">
+        <v>20375259</v>
+      </c>
+      <c r="I1528" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PLTR.xlsx
+++ b/data/PLTR.xlsx
@@ -44672,10 +44672,10 @@
         <v>197.009994506836</v>
       </c>
       <c r="D1528" t="n">
-        <v>198.720001220703</v>
+        <v>198.740005493164</v>
       </c>
       <c r="E1528" t="n">
-        <v>193.130599975586</v>
+        <v>193.130996704102</v>
       </c>
       <c r="F1528" t="n">
         <v>196.809997558594</v>
@@ -44684,9 +44684,38 @@
         <v>196.809997558594</v>
       </c>
       <c r="H1528" t="n">
-        <v>20375259</v>
+        <v>20821300</v>
       </c>
       <c r="I1528" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1529">
+      <c r="A1529" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1529" s="1" t="n">
+        <v>46324.5625</v>
+      </c>
+      <c r="C1529" t="n">
+        <v>198.36799621582</v>
+      </c>
+      <c r="D1529" t="n">
+        <v>198.509994506836</v>
+      </c>
+      <c r="E1529" t="n">
+        <v>190.369995117188</v>
+      </c>
+      <c r="F1529" t="n">
+        <v>196.419998168945</v>
+      </c>
+      <c r="G1529" t="n">
+        <v>196.419998168945</v>
+      </c>
+      <c r="H1529" t="n">
+        <v>19585592</v>
+      </c>
+      <c r="I1529" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PLTR.xlsx
+++ b/data/PLTR.xlsx
@@ -44704,7 +44704,7 @@
         <v>198.509994506836</v>
       </c>
       <c r="E1529" t="n">
-        <v>190.369995117188</v>
+        <v>190.360000610352</v>
       </c>
       <c r="F1529" t="n">
         <v>196.419998168945</v>
@@ -44713,9 +44713,38 @@
         <v>196.419998168945</v>
       </c>
       <c r="H1529" t="n">
-        <v>19585592</v>
+        <v>20102900</v>
       </c>
       <c r="I1529" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1530">
+      <c r="A1530" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1530" s="1" t="n">
+        <v>46325.5625</v>
+      </c>
+      <c r="C1530" t="n">
+        <v>193.764999389648</v>
+      </c>
+      <c r="D1530" t="n">
+        <v>193.919998168945</v>
+      </c>
+      <c r="E1530" t="n">
+        <v>183.679992675781</v>
+      </c>
+      <c r="F1530" t="n">
+        <v>184.110000610352</v>
+      </c>
+      <c r="G1530" t="n">
+        <v>184.110000610352</v>
+      </c>
+      <c r="H1530" t="n">
+        <v>26955616</v>
+      </c>
+      <c r="I1530" t="s">
         <v>9</v>
       </c>
     </row>
